--- a/tracking/13f-tracking.xlsx
+++ b/tracking/13f-tracking.xlsx
@@ -1,14 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filers to watch" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Holdings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Filers to watch" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SALP-2025-Q4" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SALP-2026-Q1" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,10 +19,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +35,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -58,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -66,6 +73,9 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1703,7 +1713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1750,7 +1760,6 @@
           <t>Buffett — owns AAPL stake worth tracking</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1768,7 +1777,6 @@
           <t>Long-duration tech conviction</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1786,7 +1794,6 @@
           <t>Concentrated tech bets</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1804,7 +1811,6 @@
           <t>AI thematic concentration</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1822,7 +1828,6 @@
           <t>AI infra heavy</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1840,7 +1845,3586 @@
           <t>Long-only tech</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Situational Awareness LP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0002045724</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Aschenbrenner — the macro thesis author; primary tracked fund</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Situational Awareness LP (CIK 0002045724) — filed 2026-02-11, period-end holdings. Values in $ (full dollars; option rows = notional value of underlying, NOT premium). Source: https://www.sec.gov/Archives/edgar/data/2045724/000204572426000002/SALP_13FQ425.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Issuer</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Value ($)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Shares Δ vs prior Q</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>% of portfolio</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BLOOM ENERGY CORP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10076022</v>
+      </c>
+      <c r="E4" t="n">
+        <v>875505552</v>
+      </c>
+      <c r="G4" s="6">
+        <f>E4/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>COREWEAVE INC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10814500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>774426345</v>
+      </c>
+      <c r="F5" s="7">
+        <f>(10814500-2314500)/2314500</f>
+        <v/>
+      </c>
+      <c r="G5" s="6">
+        <f>E5/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INTEL CORP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>20237400</v>
+      </c>
+      <c r="E6" t="n">
+        <v>746760060</v>
+      </c>
+      <c r="F6" s="7">
+        <f>(20237400-20237400)/20237400</f>
+        <v/>
+      </c>
+      <c r="G6" s="6">
+        <f>E6/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LUMENTUM HLDGS INC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1298400</v>
+      </c>
+      <c r="E7" t="n">
+        <v>478577256</v>
+      </c>
+      <c r="G7" s="6">
+        <f>E7/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>COREWEAVE INC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6098812</v>
+      </c>
+      <c r="E8" t="n">
+        <v>436735927</v>
+      </c>
+      <c r="F8" s="7">
+        <f>(6098812-4115456)/4115456</f>
+        <v/>
+      </c>
+      <c r="G8" s="6">
+        <f>E8/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CORZ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CORE SCIENTIFIC INC NEW</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>28756478</v>
+      </c>
+      <c r="E9" t="n">
+        <v>418694320</v>
+      </c>
+      <c r="F9" s="7">
+        <f>(28756478-20180534)/20180534</f>
+        <v/>
+      </c>
+      <c r="G9" s="6">
+        <f>E9/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IREN LIMITED</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8700621</v>
+      </c>
+      <c r="E10" t="n">
+        <v>328622455</v>
+      </c>
+      <c r="F10" s="7">
+        <f>(8700621-7220421)/7220421</f>
+        <v/>
+      </c>
+      <c r="G10" s="6">
+        <f>E10/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>APLD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>APPLIED DIGITAL CORP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11339060</v>
+      </c>
+      <c r="E11" t="n">
+        <v>278033751</v>
+      </c>
+      <c r="F11" s="7">
+        <f>(11339060-6064155)/6064155</f>
+        <v/>
+      </c>
+      <c r="G11" s="6">
+        <f>E11/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SANDISK CORP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1054200</v>
+      </c>
+      <c r="E12" t="n">
+        <v>250245996</v>
+      </c>
+      <c r="F12" s="7">
+        <f>(1054200-115000)/115000</f>
+        <v/>
+      </c>
+      <c r="G12" s="6">
+        <f>E12/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CIFR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CIPHER MINING INC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10469093</v>
+      </c>
+      <c r="E13" t="n">
+        <v>154523813</v>
+      </c>
+      <c r="G13" s="6">
+        <f>E13/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EQT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EQT CORP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2482225</v>
+      </c>
+      <c r="E14" t="n">
+        <v>133047260</v>
+      </c>
+      <c r="F14" s="7">
+        <f>(2482225-1217386)/1217386</f>
+        <v/>
+      </c>
+      <c r="G14" s="6">
+        <f>E14/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>COHERENT CORP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>480300</v>
+      </c>
+      <c r="E15" t="n">
+        <v>88648971</v>
+      </c>
+      <c r="F15" s="7">
+        <f>(480300-154400)/154400</f>
+        <v/>
+      </c>
+      <c r="G15" s="6">
+        <f>E15/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SEI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SOLARIS ENERGY INFRAS INC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1866500</v>
+      </c>
+      <c r="E16" t="n">
+        <v>85803005</v>
+      </c>
+      <c r="F16" s="7">
+        <f>(1866500-1150300)/1150300</f>
+        <v/>
+      </c>
+      <c r="G16" s="6">
+        <f>E16/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TSEM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TOWER SEMICONDUCTOR LTD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>723004</v>
+      </c>
+      <c r="E17" t="n">
+        <v>84895130</v>
+      </c>
+      <c r="F17" s="7">
+        <f>(723004-470600)/470600</f>
+        <v/>
+      </c>
+      <c r="G17" s="6">
+        <f>E17/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RIOT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RIOT PLATFORMS INC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6167700</v>
+      </c>
+      <c r="E18" t="n">
+        <v>78144759</v>
+      </c>
+      <c r="F18" s="7">
+        <f>(6167700-3592699)/3592699</f>
+        <v/>
+      </c>
+      <c r="G18" s="6">
+        <f>E18/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KRC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KILROY RLTY CORP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1327700</v>
+      </c>
+      <c r="E19" t="n">
+        <v>49616149</v>
+      </c>
+      <c r="G19" s="6">
+        <f>E19/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HUT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HUT 8 CORP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>860200</v>
+      </c>
+      <c r="E20" t="n">
+        <v>39517588</v>
+      </c>
+      <c r="F20" s="7">
+        <f>(860200-599000)/599000</f>
+        <v/>
+      </c>
+      <c r="G20" s="6">
+        <f>E20/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EQT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EQT CORP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>700000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>37520000</v>
+      </c>
+      <c r="G21" s="6">
+        <f>E21/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BLOOM ENERGY CORP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>408500</v>
+      </c>
+      <c r="E22" t="n">
+        <v>35494565</v>
+      </c>
+      <c r="G22" s="6">
+        <f>E22/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WYFI</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WHITEFIBER INC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1757600</v>
+      </c>
+      <c r="E23" t="n">
+        <v>27770080</v>
+      </c>
+      <c r="G23" s="6">
+        <f>E23/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PSIX</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>POWER SOLUTIONS INTL INC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>432300</v>
+      </c>
+      <c r="E24" t="n">
+        <v>24701622</v>
+      </c>
+      <c r="G24" s="6">
+        <f>E24/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BTDR</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BITDEER TECHNOLOGIES GROUP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1788000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>20043480</v>
+      </c>
+      <c r="F25" s="7">
+        <f>(1788000-929600)/929600</f>
+        <v/>
+      </c>
+      <c r="G25" s="6">
+        <f>E25/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CLSK</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CLEANSPARK INC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1640400</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16600848</v>
+      </c>
+      <c r="G26" s="6">
+        <f>E26/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>KEEL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BITFARMS LTD</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>6897100</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16208185</v>
+      </c>
+      <c r="G27" s="6">
+        <f>E27/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LBRT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LIBERTY ENERGY INC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>567200</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10470512</v>
+      </c>
+      <c r="G28" s="6">
+        <f>E28/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>INFOSYS LTD</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8910000</v>
+      </c>
+      <c r="G29" s="6">
+        <f>E29/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PUMP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PROPETRO HLDG CORP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>910300</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8656953</v>
+      </c>
+      <c r="G30" s="6">
+        <f>E30/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BW</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BABCOCK &amp; WILCOX ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1353900</v>
+      </c>
+      <c r="E31" t="n">
+        <v>8583726</v>
+      </c>
+      <c r="G31" s="6">
+        <f>E31/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>INTEL CORP</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>37</v>
+      </c>
+      <c r="G32" s="6">
+        <f>E32/SUM($E$4:$E$32)</f>
+        <v/>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>EXITED (held prior Q, gone now) — value shown is prior-Q value</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NVIDIA CORPORATION</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>298528000</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>VISTRA CORP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>252327327</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SMH(F106)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>VANECK ETF TRUST</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>195816000</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>COREWEAVE INC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>191590000</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GLXY</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GALAXY DIGITAL INC.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>92554875</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BROADCOM INC</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>75879300</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TAIWAN SEMICONDUCTOR MFG LTD</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>75408300</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CIFR-convert</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CIPHER MINING INC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>72272807</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LITE-convert</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LUMENTUM HLDGS INC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>67947696</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MICRON TECHNOLOGY INC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>50196000</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BE-convert</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BLOOM ENERGY CORP</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>43890344</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WDC-convert</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>WESTERN DIGITAL CORP</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>18347689</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BE-convert</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BLOOM ENERGY CORP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>12330306</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SEAGATE TECHNOLOGY HLDNGS PL</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>11464726</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>TOP ADDS / TRIMS (continuing positions, by |Δ$ value|; Δ$ in col E, Δshares % in col F)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="E51" t="n">
+        <v>457687020</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>3.67249945992655</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>939200</v>
+      </c>
+      <c r="E52" t="n">
+        <v>237342996</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>8.166956521739131</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>APLD</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>5274905</v>
+      </c>
+      <c r="E53" t="n">
+        <v>138922035</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>0.8698499626081457</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1983356</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-126464227</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>0.481928612527992</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>325900</v>
+      </c>
+      <c r="E55" t="n">
+        <v>72017003</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>2.110751295336788</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EQT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1264839</v>
+      </c>
+      <c r="E56" t="n">
+        <v>66784940</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>1.038979419838901</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CORZ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>8575944</v>
+      </c>
+      <c r="E57" t="n">
+        <v>56655540</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>0.4249612027114842</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TSEM</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>252404</v>
+      </c>
+      <c r="E58" t="n">
+        <v>50870750</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0.5363450913727157</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SEI</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>716200</v>
+      </c>
+      <c r="E59" t="n">
+        <v>39825514</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>0.6226201860384247</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>HUT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>261200</v>
+      </c>
+      <c r="E60" t="n">
+        <v>18666398</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>0.4360601001669449</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1480200</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-10231903</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>0.2050018967038072</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>RIOT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2575001</v>
+      </c>
+      <c r="E62" t="n">
+        <v>9775697</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>0.716731627113766</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BTDR</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>858400</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4156616</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>0.923407917383821</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Situational Awareness LP (CIK 0002045724) — filed 2026-05-18, period-end holdings. Values in $ (full dollars; option rows = notional value of underlying, NOT premium). Source: https://www.sec.gov/Archives/edgar/data/2045724/000204572426000008/salp13fq1xml.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Issuer</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Value ($)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Shares Δ vs prior Q</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>% of portfolio</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SMH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VANECK ETF TRUST</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5327900</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2042716860</v>
+      </c>
+      <c r="G4" s="6">
+        <f>E4/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NVIDIA CORPORATION</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8992300</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1568257120</v>
+      </c>
+      <c r="G5" s="6">
+        <f>E5/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ORACLE CORP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7293000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1072873230</v>
+      </c>
+      <c r="G6" s="6">
+        <f>E6/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BROADCOM INC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3251100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1006247961</v>
+      </c>
+      <c r="G7" s="6">
+        <f>E7/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ADVANCED MICRO DEVICES INC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4764100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>969160863</v>
+      </c>
+      <c r="G8" s="6">
+        <f>E8/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BLOOM ENERGY CORP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6485408</v>
+      </c>
+      <c r="E9" t="n">
+        <v>878707930</v>
+      </c>
+      <c r="F9" s="7">
+        <f>(6485408-10076022)/10076022</f>
+        <v/>
+      </c>
+      <c r="G9" s="6">
+        <f>E9/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SANDISK CORP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1140119</v>
+      </c>
+      <c r="E10" t="n">
+        <v>724363205</v>
+      </c>
+      <c r="F10" s="7">
+        <f>(1140119-1054200)/1054200</f>
+        <v/>
+      </c>
+      <c r="G10" s="6">
+        <f>E10/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MICRON TECHNOLOGY INC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1727700</v>
+      </c>
+      <c r="E11" t="n">
+        <v>583686168</v>
+      </c>
+      <c r="G11" s="6">
+        <f>E11/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>COREWEAVE INC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7177919</v>
+      </c>
+      <c r="E12" t="n">
+        <v>556073385</v>
+      </c>
+      <c r="F12" s="7">
+        <f>(7177919-6098812)/6098812</f>
+        <v/>
+      </c>
+      <c r="G12" s="6">
+        <f>E12/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TAIWAN SEMICONDUCTOR MANUFAC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1583400</v>
+      </c>
+      <c r="E13" t="n">
+        <v>535110030</v>
+      </c>
+      <c r="G13" s="6">
+        <f>E13/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ASML HLDG NV N Y REGISTRY</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>374100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>494122503</v>
+      </c>
+      <c r="G14" s="6">
+        <f>E14/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MICRON TECHNOLOGY INC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>422300000</v>
+      </c>
+      <c r="G15" s="6">
+        <f>E15/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IREN LIMITED</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11698835</v>
+      </c>
+      <c r="E16" t="n">
+        <v>401036064</v>
+      </c>
+      <c r="F16" s="7">
+        <f>(11698835-8700621)/8700621</f>
+        <v/>
+      </c>
+      <c r="G16" s="6">
+        <f>E16/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CORZ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CORE SCIENTIFIC INC NEW</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>26008473</v>
+      </c>
+      <c r="E17" t="n">
+        <v>389086756</v>
+      </c>
+      <c r="F17" s="7">
+        <f>(26008473-28756478)/28756478</f>
+        <v/>
+      </c>
+      <c r="G17" s="6">
+        <f>E17/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SANDISK CORP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>611900</v>
+      </c>
+      <c r="E18" t="n">
+        <v>388764546</v>
+      </c>
+      <c r="G18" s="6">
+        <f>E18/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TAIWAN SEMICONDUCTOR MANUFAC</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>354847500</v>
+      </c>
+      <c r="G19" s="6">
+        <f>E19/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>APLD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>APPLIED DIGITAL CORP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13478438</v>
+      </c>
+      <c r="E20" t="n">
+        <v>319978118</v>
+      </c>
+      <c r="F20" s="7">
+        <f>(13478438-11339060)/11339060</f>
+        <v/>
+      </c>
+      <c r="G20" s="6">
+        <f>E20/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>INTEL CORP</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3605400</v>
+      </c>
+      <c r="E21" t="n">
+        <v>159106302</v>
+      </c>
+      <c r="G21" s="6">
+        <f>E21/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RIOT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RIOT PLATFORMS INC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11502137</v>
+      </c>
+      <c r="E22" t="n">
+        <v>142166413</v>
+      </c>
+      <c r="F22" s="7">
+        <f>(11502137-6167700)/6167700</f>
+        <v/>
+      </c>
+      <c r="G22" s="6">
+        <f>E22/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>COREWEAVE INC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1814500</v>
+      </c>
+      <c r="E23" t="n">
+        <v>140569315</v>
+      </c>
+      <c r="F23" s="7">
+        <f>(1814500-10814500)/10814500</f>
+        <v/>
+      </c>
+      <c r="G23" s="6">
+        <f>E23/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CLSK</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CLEANSPARK INC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12276139</v>
+      </c>
+      <c r="E24" t="n">
+        <v>104469943</v>
+      </c>
+      <c r="F24" s="7">
+        <f>(12276139-1640400)/1640400</f>
+        <v/>
+      </c>
+      <c r="G24" s="6">
+        <f>E24/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SEI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SOLARIS ENERGY INFRAS INC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1105551</v>
+      </c>
+      <c r="E25" t="n">
+        <v>62474687</v>
+      </c>
+      <c r="F25" s="7">
+        <f>(1105551-1866500)/1866500</f>
+        <v/>
+      </c>
+      <c r="G25" s="6">
+        <f>E25/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BLOOM ENERGY CORP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>408500</v>
+      </c>
+      <c r="E26" t="n">
+        <v>55347665</v>
+      </c>
+      <c r="F26" s="7">
+        <f>(408500-408500)/408500</f>
+        <v/>
+      </c>
+      <c r="G26" s="6">
+        <f>E26/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>T1 ENERGY INC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>43900000</v>
+      </c>
+      <c r="G27" s="6">
+        <f>E27/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>KEEL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BITFARMS LTD</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>19875840</v>
+      </c>
+      <c r="E28" t="n">
+        <v>38757888</v>
+      </c>
+      <c r="F28" s="7">
+        <f>(19875840-6897100)/6897100</f>
+        <v/>
+      </c>
+      <c r="G28" s="6">
+        <f>E28/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BTDR</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BITDEER TECHNOLOGIES GROUP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3439450</v>
+      </c>
+      <c r="E29" t="n">
+        <v>29751243</v>
+      </c>
+      <c r="F29" s="7">
+        <f>(3439450-1788000)/1788000</f>
+        <v/>
+      </c>
+      <c r="G29" s="6">
+        <f>E29/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PSIX</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>POWER SOLUTIONS INTL INC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>432300</v>
+      </c>
+      <c r="E30" t="n">
+        <v>26318424</v>
+      </c>
+      <c r="F30" s="7">
+        <f>(432300-432300)/432300</f>
+        <v/>
+      </c>
+      <c r="G30" s="6">
+        <f>E30/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CORNING INC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>154600</v>
+      </c>
+      <c r="E31" t="n">
+        <v>21020962</v>
+      </c>
+      <c r="G31" s="6">
+        <f>E31/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WYFI</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>WHITEFIBER INC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1757600</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20933016</v>
+      </c>
+      <c r="F32" s="7">
+        <f>(1757600-1757600)/1757600</f>
+        <v/>
+      </c>
+      <c r="G32" s="6">
+        <f>E32/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ADVANCED MICRO DEVICES INC</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>99138</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20167643</v>
+      </c>
+      <c r="G33" s="6">
+        <f>E33/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BW</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BABCOCK &amp; WILCOX ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1353900</v>
+      </c>
+      <c r="E34" t="n">
+        <v>19888791</v>
+      </c>
+      <c r="F34" s="7">
+        <f>(1353900-1353900)/1353900</f>
+        <v/>
+      </c>
+      <c r="G34" s="6">
+        <f>E34/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SHAZ</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SHARONAI HOLDINGS INC</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>796108</v>
+      </c>
+      <c r="E35" t="n">
+        <v>18095535</v>
+      </c>
+      <c r="G35" s="6">
+        <f>E35/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>NEW NEW — ticker resolved 2026-06-12: SHAZ (SharonAI Holdings, fka Roth CH Holdings de-SPAC, CIK 0002068385)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PUMP</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PROPETRO HLDG CORP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>910300</v>
+      </c>
+      <c r="E36" t="n">
+        <v>13117423</v>
+      </c>
+      <c r="F36" s="7">
+        <f>(910300-910300)/910300</f>
+        <v/>
+      </c>
+      <c r="G36" s="6">
+        <f>E36/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SMH</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>VANECK ETF TRUST</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>26950</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10332630</v>
+      </c>
+      <c r="G37" s="6">
+        <f>E37/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>INTEL CORP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>202344</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8929441</v>
+      </c>
+      <c r="F38" s="7">
+        <f>(202344-1)/1</f>
+        <v/>
+      </c>
+      <c r="G38" s="6">
+        <f>E38/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TAIWAN SEMICONDUCTOR MANUFAC</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>22423</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7577853</v>
+      </c>
+      <c r="G39" s="6">
+        <f>E39/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>INFOSYS LTD</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Put</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6755000</v>
+      </c>
+      <c r="F40" s="7">
+        <f>(500000-500000)/500000</f>
+        <v/>
+      </c>
+      <c r="G40" s="6">
+        <f>E40/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>HIVE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HIVE DIGITAL TECHNOLOGIES LT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3391547</v>
+      </c>
+      <c r="E41" t="n">
+        <v>6443939</v>
+      </c>
+      <c r="G41" s="6">
+        <f>E41/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ASML HLDG NV N Y REGISTRY</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>4633</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6119405</v>
+      </c>
+      <c r="G42" s="6">
+        <f>E42/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MICRON TECHNOLOGY INC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>17362</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5865578</v>
+      </c>
+      <c r="G43" s="6">
+        <f>E43/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CORNING INC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>5283</v>
+      </c>
+      <c r="E44" t="n">
+        <v>718330</v>
+      </c>
+      <c r="G44" s="6">
+        <f>E44/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NVIDIA CORPORATION</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2855</v>
+      </c>
+      <c r="E45" t="n">
+        <v>497912</v>
+      </c>
+      <c r="G45" s="6">
+        <f>E45/SUM($E$4:$E$45)</f>
+        <v/>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>EXITED (held prior Q, gone now) — value shown is prior-Q value</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>INTEL CORP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>746760060</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LUMENTUM HLDGS INC</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>478577256</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CIFR</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CIPHER MINING INC</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>154523813</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EQT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>EQT CORP</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>133047260</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>COHERENT CORP</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>88648971</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TSEM</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TOWER SEMICONDUCTOR LTD</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>84895130</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>KRC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>KILROY RLTY CORP</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>49616149</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>HUT</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HUT 8 CORP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>39517588</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EQT</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>EQT CORP</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>37520000</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>LBRT</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LIBERTY ENERGY INC</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>10470512</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TOP ADDS / TRIMS (continuing positions, by |Δ$ value|; Δ$ in col E, Δshares % in col F)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>-9000000</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-633857030</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>-0.8322160062878543</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>85919</v>
+      </c>
+      <c r="E61" t="n">
+        <v>474117209</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>0.08150161259723013</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CRWV</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1079107</v>
+      </c>
+      <c r="E62" t="n">
+        <v>119337458</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>0.1769372461390841</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CLSK</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10635739</v>
+      </c>
+      <c r="E63" t="n">
+        <v>87869095</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>6.483625335284077</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2998214</v>
+      </c>
+      <c r="E64" t="n">
+        <v>72413609</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>0.3445977017042807</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>RIOT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>5334437</v>
+      </c>
+      <c r="E65" t="n">
+        <v>64021654</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>0.8648989088314931</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>APLD</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2139378</v>
+      </c>
+      <c r="E66" t="n">
+        <v>41944367</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>0.1886733115443432</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CORZ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>-2748005</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-29607564</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>-0.09556125058152115</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SEI</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>-760949</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-23328318</v>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>-0.4076876506830967</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>KEEL</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12978740</v>
+      </c>
+      <c r="E69" t="n">
+        <v>22549703</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>1.881767699467892</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BTDR</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1651450</v>
+      </c>
+      <c r="E70" t="n">
+        <v>9707763</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>0.9236297539149888</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>202343</v>
+      </c>
+      <c r="E71" t="n">
+        <v>8929404</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>202343</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>-3590614</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3202378</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>-0.3563523382541245</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
